--- a/JsonConverter/ExcelFiles/OO_Stage.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Stage.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>동쪽 마을의 구원</t>
+          <t>?? ??</t>
         </is>
       </c>
       <c r="C4" s="21" t="n">

--- a/JsonConverter/ExcelFiles/OO_Stage.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Stage.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>?? ??</t>
+          <t>동쪽 마을</t>
         </is>
       </c>
       <c r="C4" s="21" t="n">
@@ -734,7 +734,7 @@
       </c>
       <c r="K4" s="21" t="inlineStr">
         <is>
-          <t>채소죽을 만들어 굶주린 백성에게 전하라.</t>
+          <t>야채죽을 만들어 굶주린 백성에게 전하라.</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">

--- a/JsonConverter/ExcelFiles/OO_Stage.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Stage.xlsx
@@ -12,7 +12,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -64,8 +64,16 @@
     <font>
       <i val="1"/>
     </font>
+    <font>
+      <name val="?? ??"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -132,6 +140,11 @@
         <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border/>
@@ -182,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -233,6 +246,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -753,19 +772,65 @@
       <c r="Q4" s="18" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="18" t="n"/>
-      <c r="H5" s="18" t="n"/>
-      <c r="I5" s="18" t="n"/>
-      <c r="J5" s="18" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="18" t="n"/>
-      <c r="M5" s="18" t="n"/>
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>OO_Stage_3</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>산군의 숲</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>산군과 마주치는 숲의 장면. 떡과 꿀을 활용해 산군을 달래야 한다.</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>Images/Stages/Stage3</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>Audio/BGM/Stage3</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>OO_Stage_2</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>Ing_Carrot_01</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr"/>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>산군의 허기를 달래라</t>
+        </is>
+      </c>
+      <c r="K5" s="26" t="inlineStr">
+        <is>
+          <t>쌀과 꿀로 꿀떡을 만들어 산군에게 전하라.</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="inlineStr">
+        <is>
+          <t>OO_HoneyKoreanCake_1</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t>4th_Road_to_Stage4</t>
+        </is>
+      </c>
       <c r="N5" s="18" t="n"/>
       <c r="O5" s="18" t="n"/>
       <c r="P5" s="18" t="n"/>

--- a/JsonConverter/ExcelFiles/OO_Stage.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Stage.xlsx
@@ -2,37 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="450" yWindow="500" windowWidth="27760" windowHeight="10800" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Stage" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
-    <font>
-      <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <color rgb="FF008000"/>
-      <sz val="11"/>
-    </font>
+  <fonts count="8">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -40,40 +24,44 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="8"/>
+      <family val="2"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <i val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
     </font>
-    <font/>
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <i val="1"/>
-    </font>
-    <font>
-      <name val="?? ??"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="15">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -87,42 +75,28 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="7" tint="0.7999511703848384"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -140,14 +114,15 @@
         <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
-    <border/>
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color indexed="64"/>
@@ -161,22 +136,15 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
-    <border/>
     <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
@@ -190,73 +158,58 @@
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -470,6 +423,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -480,931 +435,1020 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="16" defaultRowHeight="12.5"/>
   <cols>
-    <col width="14" customWidth="1" style="3" min="1" max="1"/>
-    <col width="14" customWidth="1" style="3" min="2" max="2"/>
-    <col width="14" customWidth="1" style="3" min="3" max="3"/>
-    <col width="14" customWidth="1" style="3" min="4" max="4"/>
-    <col width="15" customWidth="1" style="3" min="5" max="5"/>
-    <col width="14" customWidth="1" style="3" min="6" max="6"/>
-    <col width="16" customWidth="1" style="3" min="7" max="16384"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" style="1" min="1" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22" customWidth="1" style="1" min="6" max="6"/>
+    <col width="25" customWidth="1" style="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="11"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="13"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" style="1" min="14" max="16384"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>스테이지 ID</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>스테이지 이름</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>스테이지 번호</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>스테이지 설명</t>
         </is>
       </c>
-      <c r="E1" s="22" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>배경 이미지 경로</t>
         </is>
       </c>
-      <c r="F1" s="22" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>BGM 경로</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>선행 스테이지 ID</t>
         </is>
       </c>
-      <c r="H1" s="22" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>보상 아이템 ID 목록(| 구분)</t>
         </is>
       </c>
-      <c r="I1" s="22" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>시작 대사 그룹 ID</t>
         </is>
       </c>
-      <c r="J1" s="22" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>메인 퀘스트 제목</t>
         </is>
       </c>
-      <c r="K1" s="22" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>메인 퀘스트 설명</t>
         </is>
       </c>
-      <c r="L1" s="22" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>필요 완성 음식 ID</t>
         </is>
       </c>
-      <c r="M1" s="22" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>다음 로드 그룹 ID</t>
         </is>
       </c>
-      <c r="N1" s="18" t="n"/>
-      <c r="O1" s="18" t="n"/>
-      <c r="P1" s="18" t="n"/>
-      <c r="Q1" s="18" t="n"/>
+      <c r="N1" s="11" t="n"/>
+      <c r="O1" s="11" t="n"/>
+      <c r="P1" s="11" t="n"/>
+      <c r="Q1" s="11" t="n"/>
     </row>
     <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" s="23" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="23" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L2" s="23" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="M2" s="23" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N2" s="18" t="n"/>
-      <c r="O2" s="18" t="n"/>
-      <c r="P2" s="18" t="n"/>
-      <c r="Q2" s="18" t="n"/>
-    </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="13">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="N2" s="13" t="n"/>
+      <c r="O2" s="13" t="n"/>
+      <c r="P2" s="13" t="n"/>
+      <c r="Q2" s="13" t="n"/>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="2">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>StageNumber</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>BackgroundImagePath</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>BGMPath</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>RequiredPreviousStageId</t>
         </is>
       </c>
-      <c r="H3" s="24" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>RewardItemIds</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>StartDialogueGroupId</t>
         </is>
       </c>
-      <c r="J3" s="24" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>QuestTitle</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>QuestDescription</t>
         </is>
       </c>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>RequiredCookId</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="14" t="inlineStr">
         <is>
           <t>NextRoadGroupId</t>
         </is>
       </c>
-      <c r="N3" s="18" t="n"/>
-      <c r="O3" s="18" t="n"/>
-      <c r="P3" s="18" t="n"/>
-      <c r="Q3" s="18" t="n"/>
+      <c r="N3" s="15" t="n"/>
+      <c r="O3" s="15" t="n"/>
+      <c r="P3" s="15" t="n"/>
+      <c r="Q3" s="15" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>OO_Stage_1</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>동쪽 마을</t>
         </is>
       </c>
-      <c r="C4" s="21" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>탐관오리의 수탈로 굶주린 동쪽 백성들을 위해 첫 음식을 준비하는 스테이지.</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Images/Background/Stage1</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Audio/BGM/Stage1</t>
         </is>
       </c>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="21" t="n"/>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>dialogue_stage1_start</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>동쪽 마을의 구원</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>야채죽을 만들어 굶주린 백성에게 전하라.</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>OO_VegetableSoup_1</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>2nd_Road_to_Stage2</t>
         </is>
       </c>
-      <c r="N4" s="18" t="n"/>
-      <c r="O4" s="18" t="n"/>
-      <c r="P4" s="18" t="n"/>
-      <c r="Q4" s="18" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>OO_Stage_3</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>산군의 숲</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>산군과 마주치는 숲의 장면. 떡과 꿀을 활용해 산군을 달래야 한다.</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Images/Stages/Stage3</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Audio/BGM/Stage3</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>OO_Stage_2</t>
         </is>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Ing_Carrot_01</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr"/>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>산군의 허기를 달래라</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>쌀과 꿀로 꿀떡을 만들어 산군에게 전하라.</t>
         </is>
       </c>
-      <c r="L5" s="26" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>OO_HoneyKoreanCake_1</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>4th_Road_to_Stage4</t>
         </is>
       </c>
-      <c r="N5" s="18" t="n"/>
-      <c r="O5" s="18" t="n"/>
-      <c r="P5" s="18" t="n"/>
-      <c r="Q5" s="18" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="18" t="n"/>
-      <c r="B6" s="18" t="n"/>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="18" t="n"/>
-      <c r="F6" s="18" t="n"/>
-      <c r="G6" s="18" t="n"/>
-      <c r="H6" s="18" t="n"/>
-      <c r="I6" s="18" t="n"/>
-      <c r="J6" s="18" t="n"/>
-      <c r="K6" s="18" t="n"/>
-      <c r="L6" s="18" t="n"/>
-      <c r="M6" s="18" t="n"/>
-      <c r="N6" s="18" t="n"/>
-      <c r="O6" s="18" t="n"/>
-      <c r="P6" s="18" t="n"/>
-      <c r="Q6" s="18" t="n"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>OO_Stage_2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>서쪽 도시에 있는 탐관오리의 저택</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>조선의 서쪽 풍요로운 도시에 위치한 거대한 기계식 저택. 연산군자의 통제력이 약해진 틈을 타, 조정의 명령을 거부하고 제 배만 불린 탐관오리가 백성들의 피땀을 쥐어짜 내어 건설한 탐욕의 산물이다.
+저택 내부에는 조선 제일의 기술자들을 강제로 동원해 만든 화려한 자동화 기계 장치들과 웅장한 황금빛 기어들이 밤낮없이 맞물려 돌아가고 있다. 서쪽 도시의 백성들이 극심한 굶주림에 신음하는 와중에도, 이 저택의 거대한 굴뚝에서는 기름진 산해진미를 구워대는 고기 연기와 증기가 끊이지 않고 뿜어져 나온다.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Images/Background/Stage1</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Audio/BGM/Stage1</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>dialogue_stage1_start</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>동쪽 마을의 구원</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>야채죽을 만들어 굶주린 백성에게 전하라.</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>OO_VegetableSoup_1</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>2nd_Road_to_Stage2</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="18" t="n"/>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-      <c r="H7" s="18" t="n"/>
-      <c r="I7" s="18" t="n"/>
-      <c r="J7" s="18" t="n"/>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="18" t="n"/>
-      <c r="M7" s="18" t="n"/>
-      <c r="N7" s="18" t="n"/>
-      <c r="O7" s="18" t="n"/>
-      <c r="P7" s="18" t="n"/>
-      <c r="Q7" s="18" t="n"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>OO_Stage_4</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>북쪽 토끼와 거북이</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>조선 북쪽의 농경 지대에서 토끼와 거북이의 기묘한 경주를 해결하고, 마지막 여정으로 나아가는 스테이지입니다.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Images/Stages/Stage4_1Background</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Audio/BGM/Stage4_BGM</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>OO_Stage_3</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>북쪽 들판의 경주</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>토끼를 유혹할 당근전을 만들어 경주를 끝내고 거북이에게 돌아가라.</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>OO_CarrotCake_1</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>PreFinal_Narration</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="18" t="n"/>
-      <c r="B8" s="18" t="n"/>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" s="18" t="n"/>
-      <c r="H8" s="18" t="n"/>
-      <c r="I8" s="18" t="n"/>
-      <c r="J8" s="18" t="n"/>
-      <c r="K8" s="18" t="n"/>
-      <c r="L8" s="18" t="n"/>
-      <c r="M8" s="18" t="n"/>
-      <c r="N8" s="18" t="n"/>
-      <c r="O8" s="18" t="n"/>
-      <c r="P8" s="18" t="n"/>
-      <c r="Q8" s="18" t="n"/>
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="18" t="n"/>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="18" t="n"/>
-      <c r="G9" s="18" t="n"/>
-      <c r="H9" s="18" t="n"/>
-      <c r="I9" s="18" t="n"/>
-      <c r="J9" s="18" t="n"/>
-      <c r="K9" s="18" t="n"/>
-      <c r="L9" s="18" t="n"/>
-      <c r="M9" s="18" t="n"/>
-      <c r="N9" s="18" t="n"/>
-      <c r="O9" s="18" t="n"/>
-      <c r="P9" s="18" t="n"/>
-      <c r="Q9" s="18" t="n"/>
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="18" t="n"/>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="18" t="n"/>
-      <c r="G10" s="18" t="n"/>
-      <c r="H10" s="18" t="n"/>
-      <c r="I10" s="18" t="n"/>
-      <c r="J10" s="18" t="n"/>
-      <c r="K10" s="18" t="n"/>
-      <c r="L10" s="18" t="n"/>
-      <c r="M10" s="18" t="n"/>
-      <c r="N10" s="18" t="n"/>
-      <c r="O10" s="18" t="n"/>
-      <c r="P10" s="18" t="n"/>
-      <c r="Q10" s="18" t="n"/>
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="18" t="n"/>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="18" t="n"/>
-      <c r="H11" s="18" t="n"/>
-      <c r="I11" s="18" t="n"/>
-      <c r="J11" s="18" t="n"/>
-      <c r="K11" s="18" t="n"/>
-      <c r="L11" s="18" t="n"/>
-      <c r="M11" s="18" t="n"/>
-      <c r="N11" s="18" t="n"/>
-      <c r="O11" s="18" t="n"/>
-      <c r="P11" s="18" t="n"/>
-      <c r="Q11" s="18" t="n"/>
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="18" t="n"/>
-      <c r="B12" s="18" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="18" t="n"/>
-      <c r="H12" s="18" t="n"/>
-      <c r="I12" s="18" t="n"/>
-      <c r="J12" s="18" t="n"/>
-      <c r="K12" s="18" t="n"/>
-      <c r="L12" s="18" t="n"/>
-      <c r="M12" s="18" t="n"/>
-      <c r="N12" s="18" t="n"/>
-      <c r="O12" s="18" t="n"/>
-      <c r="P12" s="18" t="n"/>
-      <c r="Q12" s="18" t="n"/>
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="18" t="n"/>
-      <c r="B13" s="18" t="n"/>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="18" t="n"/>
-      <c r="G13" s="18" t="n"/>
-      <c r="H13" s="18" t="n"/>
-      <c r="I13" s="18" t="n"/>
-      <c r="J13" s="18" t="n"/>
-      <c r="K13" s="18" t="n"/>
-      <c r="L13" s="18" t="n"/>
-      <c r="M13" s="18" t="n"/>
-      <c r="N13" s="18" t="n"/>
-      <c r="O13" s="18" t="n"/>
-      <c r="P13" s="18" t="n"/>
-      <c r="Q13" s="18" t="n"/>
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="18" t="n"/>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
-      <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
-      <c r="J14" s="18" t="n"/>
-      <c r="K14" s="18" t="n"/>
-      <c r="L14" s="18" t="n"/>
-      <c r="M14" s="18" t="n"/>
-      <c r="N14" s="18" t="n"/>
-      <c r="O14" s="18" t="n"/>
-      <c r="P14" s="18" t="n"/>
-      <c r="Q14" s="18" t="n"/>
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="3" t="n"/>
+      <c r="Q14" s="3" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="18" t="n"/>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="18" t="n"/>
-      <c r="H15" s="18" t="n"/>
-      <c r="I15" s="18" t="n"/>
-      <c r="J15" s="18" t="n"/>
-      <c r="K15" s="18" t="n"/>
-      <c r="L15" s="18" t="n"/>
-      <c r="M15" s="18" t="n"/>
-      <c r="N15" s="18" t="n"/>
-      <c r="O15" s="18" t="n"/>
-      <c r="P15" s="18" t="n"/>
-      <c r="Q15" s="18" t="n"/>
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="18" t="n"/>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
-      <c r="H16" s="18" t="n"/>
-      <c r="I16" s="18" t="n"/>
-      <c r="J16" s="18" t="n"/>
-      <c r="K16" s="18" t="n"/>
-      <c r="L16" s="18" t="n"/>
-      <c r="M16" s="18" t="n"/>
-      <c r="N16" s="18" t="n"/>
-      <c r="O16" s="18" t="n"/>
-      <c r="P16" s="18" t="n"/>
-      <c r="Q16" s="18" t="n"/>
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="3" t="n"/>
+      <c r="Q16" s="3" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="18" t="n"/>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
-      <c r="H17" s="18" t="n"/>
-      <c r="I17" s="18" t="n"/>
-      <c r="J17" s="18" t="n"/>
-      <c r="K17" s="18" t="n"/>
-      <c r="L17" s="18" t="n"/>
-      <c r="M17" s="18" t="n"/>
-      <c r="N17" s="18" t="n"/>
-      <c r="O17" s="18" t="n"/>
-      <c r="P17" s="18" t="n"/>
-      <c r="Q17" s="18" t="n"/>
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="18" t="n"/>
-      <c r="B18" s="18" t="n"/>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" s="18" t="n"/>
-      <c r="H18" s="18" t="n"/>
-      <c r="I18" s="18" t="n"/>
-      <c r="J18" s="18" t="n"/>
-      <c r="K18" s="18" t="n"/>
-      <c r="L18" s="18" t="n"/>
-      <c r="M18" s="18" t="n"/>
-      <c r="N18" s="18" t="n"/>
-      <c r="O18" s="18" t="n"/>
-      <c r="P18" s="18" t="n"/>
-      <c r="Q18" s="18" t="n"/>
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="3" t="n"/>
+      <c r="Q18" s="3" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="18" t="n"/>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="18" t="n"/>
-      <c r="H19" s="18" t="n"/>
-      <c r="I19" s="18" t="n"/>
-      <c r="J19" s="18" t="n"/>
-      <c r="K19" s="18" t="n"/>
-      <c r="L19" s="18" t="n"/>
-      <c r="M19" s="18" t="n"/>
-      <c r="N19" s="18" t="n"/>
-      <c r="O19" s="18" t="n"/>
-      <c r="P19" s="18" t="n"/>
-      <c r="Q19" s="18" t="n"/>
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="n"/>
+      <c r="Q19" s="3" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="18" t="n"/>
-      <c r="B20" s="18" t="n"/>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="18" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="18" t="n"/>
-      <c r="H20" s="18" t="n"/>
-      <c r="I20" s="18" t="n"/>
-      <c r="J20" s="18" t="n"/>
-      <c r="K20" s="18" t="n"/>
-      <c r="L20" s="18" t="n"/>
-      <c r="M20" s="18" t="n"/>
-      <c r="N20" s="18" t="n"/>
-      <c r="O20" s="18" t="n"/>
-      <c r="P20" s="18" t="n"/>
-      <c r="Q20" s="18" t="n"/>
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="3" t="n"/>
+      <c r="P20" s="3" t="n"/>
+      <c r="Q20" s="3" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="18" t="n"/>
-      <c r="B21" s="18" t="n"/>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="18" t="n"/>
-      <c r="H21" s="18" t="n"/>
-      <c r="I21" s="18" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="18" t="n"/>
-      <c r="L21" s="18" t="n"/>
-      <c r="M21" s="18" t="n"/>
-      <c r="N21" s="18" t="n"/>
-      <c r="O21" s="18" t="n"/>
-      <c r="P21" s="18" t="n"/>
-      <c r="Q21" s="18" t="n"/>
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="18" t="n"/>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="18" t="n"/>
-      <c r="H22" s="18" t="n"/>
-      <c r="I22" s="18" t="n"/>
-      <c r="J22" s="18" t="n"/>
-      <c r="K22" s="18" t="n"/>
-      <c r="L22" s="18" t="n"/>
-      <c r="M22" s="18" t="n"/>
-      <c r="N22" s="18" t="n"/>
-      <c r="O22" s="18" t="n"/>
-      <c r="P22" s="18" t="n"/>
-      <c r="Q22" s="18" t="n"/>
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="n"/>
+      <c r="Q22" s="3" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="18" t="n"/>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="18" t="n"/>
-      <c r="N23" s="18" t="n"/>
-      <c r="O23" s="18" t="n"/>
-      <c r="P23" s="18" t="n"/>
-      <c r="Q23" s="18" t="n"/>
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="18" t="n"/>
-      <c r="B24" s="18" t="n"/>
-      <c r="C24" s="18" t="n"/>
-      <c r="D24" s="18" t="n"/>
-      <c r="E24" s="18" t="n"/>
-      <c r="F24" s="18" t="n"/>
-      <c r="G24" s="18" t="n"/>
-      <c r="H24" s="18" t="n"/>
-      <c r="I24" s="18" t="n"/>
-      <c r="J24" s="18" t="n"/>
-      <c r="K24" s="18" t="n"/>
-      <c r="L24" s="18" t="n"/>
-      <c r="M24" s="18" t="n"/>
-      <c r="N24" s="18" t="n"/>
-      <c r="O24" s="18" t="n"/>
-      <c r="P24" s="18" t="n"/>
-      <c r="Q24" s="18" t="n"/>
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3" t="n"/>
+      <c r="O24" s="3" t="n"/>
+      <c r="P24" s="3" t="n"/>
+      <c r="Q24" s="3" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="18" t="n"/>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="18" t="n"/>
-      <c r="N25" s="18" t="n"/>
-      <c r="O25" s="18" t="n"/>
-      <c r="P25" s="18" t="n"/>
-      <c r="Q25" s="18" t="n"/>
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="n"/>
+      <c r="Q25" s="3" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="18" t="n"/>
-      <c r="B26" s="18" t="n"/>
-      <c r="C26" s="18" t="n"/>
-      <c r="D26" s="18" t="n"/>
-      <c r="E26" s="18" t="n"/>
-      <c r="F26" s="18" t="n"/>
-      <c r="G26" s="18" t="n"/>
-      <c r="H26" s="18" t="n"/>
-      <c r="I26" s="18" t="n"/>
-      <c r="J26" s="18" t="n"/>
-      <c r="K26" s="18" t="n"/>
-      <c r="L26" s="18" t="n"/>
-      <c r="M26" s="18" t="n"/>
-      <c r="N26" s="18" t="n"/>
-      <c r="O26" s="18" t="n"/>
-      <c r="P26" s="18" t="n"/>
-      <c r="Q26" s="18" t="n"/>
+      <c r="A26" s="3" t="n"/>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3" t="n"/>
+      <c r="O26" s="3" t="n"/>
+      <c r="P26" s="3" t="n"/>
+      <c r="Q26" s="3" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="18" t="n"/>
-      <c r="B27" s="18" t="n"/>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="18" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="18" t="n"/>
-      <c r="G27" s="18" t="n"/>
-      <c r="H27" s="18" t="n"/>
-      <c r="I27" s="18" t="n"/>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="18" t="n"/>
-      <c r="L27" s="18" t="n"/>
-      <c r="M27" s="18" t="n"/>
-      <c r="N27" s="18" t="n"/>
-      <c r="O27" s="18" t="n"/>
-      <c r="P27" s="18" t="n"/>
-      <c r="Q27" s="18" t="n"/>
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="n"/>
+      <c r="Q27" s="3" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="18" t="n"/>
-      <c r="B28" s="18" t="n"/>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-      <c r="G28" s="18" t="n"/>
-      <c r="H28" s="18" t="n"/>
-      <c r="I28" s="18" t="n"/>
-      <c r="J28" s="18" t="n"/>
-      <c r="K28" s="18" t="n"/>
-      <c r="L28" s="18" t="n"/>
-      <c r="M28" s="18" t="n"/>
-      <c r="N28" s="18" t="n"/>
-      <c r="O28" s="18" t="n"/>
-      <c r="P28" s="18" t="n"/>
-      <c r="Q28" s="18" t="n"/>
+      <c r="A28" s="3" t="n"/>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3" t="n"/>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="3" t="n"/>
+      <c r="Q28" s="3" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="18" t="n"/>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="18" t="n"/>
-      <c r="I29" s="18" t="n"/>
-      <c r="J29" s="18" t="n"/>
-      <c r="K29" s="18" t="n"/>
-      <c r="L29" s="18" t="n"/>
-      <c r="M29" s="18" t="n"/>
-      <c r="N29" s="18" t="n"/>
-      <c r="O29" s="18" t="n"/>
-      <c r="P29" s="18" t="n"/>
-      <c r="Q29" s="18" t="n"/>
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
+      <c r="O29" s="3" t="n"/>
+      <c r="P29" s="3" t="n"/>
+      <c r="Q29" s="3" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="18" t="n"/>
-      <c r="B30" s="18" t="n"/>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="18" t="n"/>
-      <c r="E30" s="18" t="n"/>
-      <c r="F30" s="18" t="n"/>
-      <c r="G30" s="18" t="n"/>
-      <c r="H30" s="18" t="n"/>
-      <c r="I30" s="18" t="n"/>
-      <c r="J30" s="18" t="n"/>
-      <c r="K30" s="18" t="n"/>
-      <c r="L30" s="18" t="n"/>
-      <c r="M30" s="18" t="n"/>
-      <c r="N30" s="18" t="n"/>
-      <c r="O30" s="18" t="n"/>
-      <c r="P30" s="18" t="n"/>
-      <c r="Q30" s="18" t="n"/>
+      <c r="A30" s="3" t="n"/>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="3" t="n"/>
+      <c r="Q30" s="3" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="18" t="n"/>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="18" t="n"/>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="18" t="n"/>
-      <c r="N31" s="18" t="n"/>
-      <c r="O31" s="18" t="n"/>
-      <c r="P31" s="18" t="n"/>
-      <c r="Q31" s="18" t="n"/>
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
+      <c r="O31" s="3" t="n"/>
+      <c r="P31" s="3" t="n"/>
+      <c r="Q31" s="3" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="18" t="n"/>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="18" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="18" t="n"/>
-      <c r="G32" s="18" t="n"/>
-      <c r="H32" s="18" t="n"/>
-      <c r="I32" s="18" t="n"/>
-      <c r="J32" s="18" t="n"/>
-      <c r="K32" s="18" t="n"/>
-      <c r="L32" s="18" t="n"/>
-      <c r="M32" s="18" t="n"/>
-      <c r="N32" s="18" t="n"/>
-      <c r="O32" s="18" t="n"/>
-      <c r="P32" s="18" t="n"/>
-      <c r="Q32" s="18" t="n"/>
+      <c r="A32" s="3" t="n"/>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
+      <c r="N32" s="3" t="n"/>
+      <c r="O32" s="3" t="n"/>
+      <c r="P32" s="3" t="n"/>
+      <c r="Q32" s="3" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="18" t="n"/>
-      <c r="B33" s="18" t="n"/>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="18" t="n"/>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="18" t="n"/>
-      <c r="L33" s="18" t="n"/>
-      <c r="M33" s="18" t="n"/>
-      <c r="N33" s="18" t="n"/>
-      <c r="O33" s="18" t="n"/>
-      <c r="P33" s="18" t="n"/>
-      <c r="Q33" s="18" t="n"/>
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="3" t="n"/>
+      <c r="Q33" s="3" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="18" t="n"/>
-      <c r="B34" s="18" t="n"/>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="18" t="n"/>
-      <c r="E34" s="18" t="n"/>
-      <c r="F34" s="18" t="n"/>
-      <c r="G34" s="18" t="n"/>
-      <c r="H34" s="18" t="n"/>
-      <c r="I34" s="18" t="n"/>
-      <c r="J34" s="18" t="n"/>
-      <c r="K34" s="18" t="n"/>
-      <c r="L34" s="18" t="n"/>
-      <c r="M34" s="18" t="n"/>
-      <c r="N34" s="18" t="n"/>
-      <c r="O34" s="18" t="n"/>
-      <c r="P34" s="18" t="n"/>
-      <c r="Q34" s="18" t="n"/>
+      <c r="A34" s="3" t="n"/>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="n"/>
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="3" t="n"/>
+      <c r="Q34" s="3" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="18" t="n"/>
-      <c r="B35" s="18" t="n"/>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="18" t="n"/>
-      <c r="I35" s="18" t="n"/>
-      <c r="J35" s="18" t="n"/>
-      <c r="K35" s="18" t="n"/>
-      <c r="L35" s="18" t="n"/>
-      <c r="M35" s="18" t="n"/>
-      <c r="N35" s="18" t="n"/>
-      <c r="O35" s="18" t="n"/>
-      <c r="P35" s="18" t="n"/>
-      <c r="Q35" s="18" t="n"/>
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="3" t="n"/>
+      <c r="Q35" s="3" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1"/>
     <row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Stage.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Stage.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>탐관오리의 수탈로 굶주린 동쪽 백성들을 위해 첫 음식을 준비하는 스테이지.</t>
+          <t>동쪽 마을은 모란의 첫 번째 본격 임무가 시작되는 장소입니다. 탐관오리의 수탈로 굶주린 백성들을 위해 쌀과 채소를 모아 따뜻한 야채죽을 준비합니다.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>산군과 마주치는 숲의 장면. 떡과 꿀을 활용해 산군을 달래야 한다.</t>
+          <t>산군의 숲은 위협적인 산군과 마주치는 긴장감 있는 장소입니다. 절구로 떡을 만들고 꿀과 조합해 꿀떡을 완성해야 산군의 분노를 달랠 수 있습니다.</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -811,8 +811,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>조선의 서쪽 풍요로운 도시에 위치한 거대한 기계식 저택. 연산군자의 통제력이 약해진 틈을 타, 조정의 명령을 거부하고 제 배만 불린 탐관오리가 백성들의 피땀을 쥐어짜 내어 건설한 탐욕의 산물이다.
-저택 내부에는 조선 제일의 기술자들을 강제로 동원해 만든 화려한 자동화 기계 장치들과 웅장한 황금빛 기어들이 밤낮없이 맞물려 돌아가고 있다. 서쪽 도시의 백성들이 극심한 굶주림에 신음하는 와중에도, 이 저택의 거대한 굴뚝에서는 기름진 산해진미를 구워대는 고기 연기와 증기가 끊이지 않고 뿜어져 나온다.</t>
+          <t>서쪽 도시는 탐관오리의 기계식 저택이 자리한 장소입니다. 화려한 장치와 탐욕스러운 분위기 속에서 모란은 새로운 재료와 조력자를 만나 다음 여정으로 나아갑니다.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -873,7 +872,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>조선 북쪽의 농경 지대에서 토끼와 거북이의 기묘한 경주를 해결하고, 마지막 여정으로 나아가는 스테이지입니다.</t>
+          <t>북쪽 농경지대는 토끼와 거북이의 마지막 의뢰가 펼쳐지는 장소입니다. 모란은 당근전을 만들어 토끼를 유혹하고, 모든 스테이지 임무를 마무리합니다.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
